--- a/Design/Tables/GameAssets.xlsx
+++ b/Design/Tables/GameAssets.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameAssets" sheetId="1" r:id="Rc6106575affe41ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameAssets" sheetId="1" r:id="R525e8fb6cf294d60"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -251,92 +251,145 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:sheetFormatPr defaultRowHeight="15"/>
-  <ns0:cols>
-    <ns0:col min="1" max="1" width="28.3799991607666" hidden="0" customWidth="1"/>
-    <ns0:col min="2" max="2" width="92.75" hidden="0" customWidth="1"/>
-    <ns0:col min="3" max="3" width="33.630001068115234" hidden="0" customWidth="1"/>
-  </ns0:cols>
-  <ns0:sheetData>
-    <ns0:row r="1" ht="15" hidden="0" customHeight="1">
-      <ns0:c r="A1" s="2" t="str">
-        <ns0:v>Name</ns0:v>
-      </ns0:c>
-      <ns0:c r="B1" s="2" t="str">
-        <ns0:v>Path</ns0:v>
-      </ns0:c>
-      <ns0:c r="C1" s="2" t="str">
-        <ns0:v>Description</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="2" ht="15" hidden="0" customHeight="1">
-      <ns0:c r="A2" s="1" t="str">
-        <ns0:v>ID&lt;name&gt;</ns0:v>
-      </ns0:c>
-      <ns0:c r="B2" s="1" t="str">
-        <ns0:v>path</ns0:v>
-      </ns0:c>
-      <ns0:c r="C2" s="1" t="str">
-        <ns0:v>string</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="3" ht="15" hidden="0" customHeight="1">
-      <ns0:c r="A3" s="1" t="str">
-        <ns0:v>all</ns0:v>
-      </ns0:c>
-      <ns0:c r="B3" s="1" t="str">
-        <ns0:v>client</ns0:v>
-      </ns0:c>
-      <ns0:c r="C3" s="1" t="str">
-        <ns0:v>client</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="4" ht="15" hidden="0" customHeight="1">
-      <ns0:c r="A4" s="1" t="str">
-        <ns0:v>Boss</ns0:v>
-      </ns0:c>
-      <ns0:c r="B4" s="1" t="str">
-        <ns0:v/>
-      </ns0:c>
-      <ns0:c r="C4" s="1" t="str">
-        <ns0:v>보스 전투 설정</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="5" ht="15" hidden="0" customHeight="1">
-      <ns0:c r="A5" s="1" t="str">
-        <ns0:v>CombatFX</ns0:v>
-      </ns0:c>
-      <ns0:c r="B5" s="1" t="str">
-        <ns0:v/>
-      </ns0:c>
-      <ns0:c r="C5" s="1" t="str">
-        <ns0:v>전투 이펙트 설정</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="6" ht="15" hidden="0" customHeight="1">
-      <ns0:c r="A6" s="1" t="str">
-        <ns0:v>PlayerCombat</ns0:v>
-      </ns0:c>
-      <ns0:c r="B6" s="1" t="str">
-        <ns0:v/>
-      </ns0:c>
-      <ns0:c r="C6" s="1" t="str">
-        <ns0:v>플레이어 전투 설정</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="7" ht="15" hidden="0" customHeight="1">
-      <ns0:c r="A7" s="1" t="str">
-        <ns0:v>Player</ns0:v>
-      </ns0:c>
-      <ns0:c r="B7" s="1" t="str">
-        <ns0:v/>
-      </ns0:c>
-      <ns0:c r="C7" s="1" t="str">
-        <ns0:v>플레이어 클래스</ns0:v>
-      </ns0:c>
-    </ns0:row>
-  </ns0:sheetData>
-  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</ns0:worksheet>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="155" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="33.630001068115234" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>Name</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="str">
+        <x:v>Path</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="str">
+        <x:v>Description</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="1" t="str">
+        <x:v>ID&lt;name&gt;</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="str">
+        <x:v>path</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="str">
+        <x:v>string</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="1" t="str">
+        <x:v>all</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="str">
+        <x:v>client</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="1" t="str">
+        <x:v>Boss</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="str">
+        <x:v>/Game/DrSample/Combat/DA_DrSampleEnemy.DA_DrSampleEnemy</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="str">
+        <x:v>보스 전투 설정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="1" t="str">
+        <x:v>CombatFX</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="str"/>
+      <x:c r="C5" s="1" t="str">
+        <x:v>전투 이펙트 설정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="1" t="str">
+        <x:v>PlayerCombat</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="str">
+        <x:v>/Game/DrSample/Combat/DA_DrSamplePlayerCombat.DA_DrSamplePlayerCombat</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="str">
+        <x:v>플레이어 전투 설정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="1" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="str">
+        <x:v>/Game/DrSample/Characters/B_DrSamplePlayer.B_DrSamplePlayer_C</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="str">
+        <x:v>플레이어 클래스</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>BossAnim_Idle</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>/Game/Characters/Heroes/Mannequin/Animations/Locomotion/Unarmed/MM_Unarmed_Idle_Ready.MM_Unarmed_Idle_Ready</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>샘플 적 애니메이션</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>BossAnim_Move</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>/Game/Characters/Heroes/Mannequin/Animations/Locomotion/Unarmed/MM_Unarmed_Jog_Fwd.MM_Unarmed_Jog_Fwd</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>샘플 적 애니메이션</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>BossAnim_Hit</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>/Game/Characters/Heroes/Mannequin/Animations/Actions/MM_HitReact_Front_Lgt_01.MM_HitReact_Front_Lgt_01</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>샘플 적 애니메이션</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>BossAnim_Death</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>/Game/Characters/Heroes/Mannequin/Animations/Actions/MM_Death_Front_01.MM_Death_Front_01</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>샘플 적 애니메이션</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>BossAnim_Attack</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>/Game/Characters/Heroes/Mannequin/Animations/Actions/MM_Pistol_Melee.MM_Pistol_Melee</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>샘플 적 애니메이션</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>